--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486531_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486531_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4684</v>
+        <v>5.5271</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2063</v>
+        <v>4.4634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2621</v>
+        <v>1.0637</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6975</v>
+        <v>4.2804</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8241000000000001</v>
+        <v>1.5966</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8734</v>
+        <v>2.6838</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5092</v>
+        <v>4.3571</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7387</v>
+        <v>2.0804</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2295</v>
+        <v>2.2766</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1882</v>
+        <v>-0.0767</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0854</v>
+        <v>-0.4838</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1029</v>
+        <v>0.4072</v>
       </c>
       <c r="P2" t="n">
         <v>0.87</v>
@@ -610,28 +610,28 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5807</v>
+        <v>0.1815</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8051</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7756</v>
+        <v>0.2704</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7151</v>
+        <v>0.1952</v>
       </c>
       <c r="W2" t="n">
-        <v>4.9103</v>
+        <v>0.1952</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8746</v>
+        <v>4.3732</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8108</v>
+        <v>4.6042</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0637</v>
+        <v>-0.231</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2804</v>
+        <v>-1.6975</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5966</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6838</v>
+        <v>-0.8734</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3571</v>
+        <v>-0.5092</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0804</v>
+        <v>-0.7387</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2766</v>
+        <v>0.2295</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0767</v>
+        <v>-1.1882</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4838</v>
+        <v>-0.0854</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4072</v>
+        <v>-1.1029</v>
       </c>
       <c r="P3" t="n">
         <v>0.87</v>
@@ -688,28 +688,28 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4711</v>
+        <v>0.4855</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.2031</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2704</v>
+        <v>0.2824</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1952</v>
+        <v>4.7151</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>4.9103</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4825</v>
+        <v>3.6934</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0156</v>
+        <v>3.6694</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4669</v>
+        <v>0.024</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4889</v>
+        <v>2.1113</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.9336</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1466</v>
+        <v>1.1778</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0667</v>
+        <v>3.2175</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1246</v>
+        <v>1.5329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1912</v>
+        <v>1.6846</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4222</v>
+        <v>-1.1062</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7601</v>
+        <v>-0.5994</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3379</v>
+        <v>-0.5068</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0588</v>
+        <v>0.4945</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9287</v>
+        <v>0.4518</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1301</v>
+        <v>0.0427</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9302</v>
+        <v>3.3007</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0912</v>
+        <v>1.7542</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1609</v>
+        <v>1.5465</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1113</v>
+        <v>1.0713</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9336</v>
+        <v>1.241</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1778</v>
+        <v>-0.1697</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2175</v>
+        <v>1.2834</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5329</v>
+        <v>0.6482</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6846</v>
+        <v>0.6352</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1062</v>
+        <v>-0.2121</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5994</v>
+        <v>0.5927</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5068</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.0342</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8736</v>
+        <v>0.4506</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1423</v>
+        <v>-0.4164</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7149</v>
+        <v>3.0087</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7231</v>
+        <v>1.035</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9917</v>
+        <v>1.9737</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0713</v>
+        <v>0.4889</v>
       </c>
       <c r="H6" t="n">
-        <v>1.241</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1697</v>
+        <v>-0.1466</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2834</v>
+        <v>0.0667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6482</v>
+        <v>-0.1246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6352</v>
+        <v>0.1912</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2121</v>
+        <v>0.4222</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5927</v>
+        <v>0.7601</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.3379</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5516</v>
+        <v>1.585</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5804</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9712</v>
+        <v>0.6369</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3252</v>
+        <v>0.9347</v>
       </c>
       <c r="W6" t="n">
         <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8739</v>
+        <v>0.7056</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2283</v>
+        <v>-0.5816</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1022</v>
+        <v>1.2872</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4313</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.718</v>
+        <v>1.5496</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4012</v>
+        <v>1.0479</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3168</v>
+        <v>0.5017</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1123</v>
+        <v>0.011</v>
       </c>
       <c r="E8" t="n">
         <v>-0.608</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4957</v>
+        <v>0.619</v>
       </c>
       <c r="G8" t="n">
         <v>-0.275</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1627</v>
+        <v>0.286</v>
       </c>
       <c r="T8" t="n">
         <v>0.0805</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0822</v>
+        <v>0.2055</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1594</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2517</v>
+        <v>-1.7794</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0923</v>
+        <v>0.9381</v>
       </c>
       <c r="G9" t="n">
         <v>-0.039</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5979</v>
+        <v>-0.2797</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8099</v>
+        <v>-0.3377</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2121</v>
+        <v>0.058</v>
       </c>
       <c r="V9" t="n">
         <v>0.5649999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1866</v>
+        <v>-1.254</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0458</v>
+        <v>-0.4429</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2324</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8034</v>
+        <v>-1.0211</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3285</v>
+        <v>-0.1127</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4749</v>
+        <v>-0.9084</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.08459999999999999</v>
+        <v>0.2492</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1611</v>
+        <v>-0.6903</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0765</v>
+        <v>0.9395</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7188</v>
+        <v>-1.2703</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1674</v>
+        <v>0.5776</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5514</v>
+        <v>-1.8479</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2041</v>
+        <v>0.6796</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0227</v>
+        <v>0.6129</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1815</v>
+        <v>0.0667</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.13</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7411</v>
+        <v>-1.5608</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6271</v>
+        <v>-1.4468</v>
       </c>
       <c r="F11" t="n">
         <v>-0.114</v>
@@ -1312,10 +1312,10 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.286</v>
+        <v>-0.1057</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.137</v>
+        <v>0.0433</v>
       </c>
       <c r="U11" t="n">
         <v>-0.149</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4815</v>
+        <v>-1.7634</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3622</v>
+        <v>-0.5311</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1193</v>
+        <v>-1.2324</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0211</v>
+        <v>-0.8034</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1127</v>
+        <v>-0.3285</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9084</v>
+        <v>-0.4749</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2492</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6903</v>
+        <v>-0.1611</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9395</v>
+        <v>0.0765</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2703</v>
+        <v>-0.7188</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5776</v>
+        <v>-0.1674</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8479</v>
+        <v>-0.5514</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.548</v>
+        <v>0.6273</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3064</v>
+        <v>0.4458</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2415</v>
+        <v>0.1815</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>-0.9347</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.048</v>
+        <v>-1.8722</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1259</v>
+        <v>-0.7343</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9221</v>
+        <v>-1.1378</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6696</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2484</v>
+        <v>0.9274</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9229000000000001</v>
+        <v>0.4687</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6745</v>
+        <v>0.4587</v>
       </c>
       <c r="V13" t="n">
         <v>-1.13</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.6156</v>
+        <v>13.3281</v>
       </c>
       <c r="E14" t="n">
-        <v>7.689599999999999</v>
+        <v>9.402099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.925900000000001</v>
+        <v>3.926</v>
       </c>
       <c r="G14" t="n">
         <v>0.3424000000000005</v>
@@ -1519,10 +1519,10 @@
         <v>2.3348</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5871</v>
+        <v>5.587100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.2066</v>
+        <v>-3.206600000000001</v>
       </c>
       <c r="L14" t="n">
         <v>8.7936</v>
@@ -1546,13 +1546,13 @@
         <v>11.9626</v>
       </c>
       <c r="S14" t="n">
-        <v>4.752700000000001</v>
+        <v>6.465199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6138</v>
+        <v>4.326099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1392</v>
+        <v>2.1391</v>
       </c>
       <c r="V14" t="n">
         <v>4.345299999999999</v>
@@ -1561,7 +1561,7 @@
         <v>9.276299999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.930999999999999</v>
+        <v>-4.931</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4362</v>
+        <v>2.8992</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7134</v>
+        <v>2.2722</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2772</v>
+        <v>0.6271</v>
       </c>
       <c r="G15" t="n">
         <v>2.8478</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.5416</v>
+        <v>-1.0785</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3579</v>
+        <v>-0.7991</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1837</v>
+        <v>-0.2794</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3715</v>
+        <v>0.963</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2487</v>
+        <v>1.5782</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8773</v>
+        <v>-0.6152</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3138</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3802</v>
+        <v>-0.0282</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4627</v>
+        <v>-0.2079</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0824</v>
+        <v>0.1796</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5748</v>
+        <v>0.8996</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9419999999999999</v>
+        <v>-0.4431</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3672</v>
+        <v>1.3427</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7256</v>
+        <v>0.0476</v>
       </c>
       <c r="H17" t="n">
-        <v>0.52</v>
+        <v>1.1951</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2056</v>
+        <v>-1.1475</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8445</v>
+        <v>0.2238</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.949</v>
       </c>
       <c r="L17" t="n">
-        <v>1.224</v>
+        <v>-0.7251</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1188</v>
+        <v>-0.1762</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1004</v>
+        <v>0.2461</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0184</v>
+        <v>-0.4224</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9367</v>
+        <v>-0.018</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4026</v>
+        <v>-0.4494</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5341</v>
+        <v>0.4314</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5271</v>
+        <v>-0.1019</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6666</v>
+        <v>-2.3493</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1937</v>
+        <v>2.2474</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0476</v>
+        <v>1.0387</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1951</v>
+        <v>-0.1247</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1475</v>
+        <v>1.1634</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2238</v>
+        <v>-1.1096</v>
       </c>
       <c r="K18" t="n">
-        <v>0.949</v>
+        <v>-1.3989</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7251</v>
+        <v>0.2893</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1762</v>
+        <v>2.1483</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2461</v>
+        <v>1.2741</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4224</v>
+        <v>0.8741</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3906</v>
+        <v>-0.313</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2824</v>
+        <v>-0.3359</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9947</v>
+        <v>-0.1856</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9081</v>
+        <v>0.495</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9134</v>
+        <v>-0.6805</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0387</v>
+        <v>0.7256</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1247</v>
+        <v>0.52</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1634</v>
+        <v>0.2056</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1096</v>
+        <v>1.8445</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3989</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2893</v>
+        <v>1.224</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1483</v>
+        <v>-1.1188</v>
       </c>
       <c r="N19" t="n">
-        <v>1.2741</v>
+        <v>-0.1004</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8741</v>
+        <v>-1.0184</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9576</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2058</v>
+        <v>0.1763</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.536</v>
+        <v>-0.0445</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6698</v>
+        <v>0.2208</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3319</v>
+        <v>-0.831</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8176</v>
+        <v>-1.0411</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5143</v>
+        <v>0.2102</v>
       </c>
       <c r="G20" t="n">
         <v>0.1628</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0396</v>
+        <v>-0.5387</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1406</v>
+        <v>-0.0829</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1802</v>
+        <v>-0.4558</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3252</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8283</v>
+        <v>-1.2425</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0303</v>
+        <v>-0.5833</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.798</v>
+        <v>-0.6592</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4187</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7571</v>
+        <v>-0.1712</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0839</v>
+        <v>-0.6369</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3268</v>
+        <v>0.4656</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2916</v>
+        <v>-1.3179</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3936</v>
+        <v>2.0642</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6852</v>
+        <v>-3.3821</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8653999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7312</v>
+        <v>0.2424</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1274</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0667</v>
+        <v>0.3698</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>T. ROTEGARD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6218</v>
+        <v>-2.9756</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9145</v>
+        <v>-2.7184</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5362</v>
+        <v>-0.2573</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3003</v>
+        <v>-1.5327</v>
       </c>
       <c r="H23" t="n">
-        <v>0.286</v>
+        <v>0.0395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0143</v>
+        <v>-1.5722</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8216</v>
+        <v>-1.2259</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5538</v>
+        <v>-0.6721</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2677</v>
+        <v>-0.5538</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5213</v>
+        <v>-0.3068</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2679</v>
+        <v>0.7116</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2534</v>
+        <v>-1.0184</v>
       </c>
       <c r="P23" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R23" t="n">
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5979</v>
+        <v>-0.7904</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6802</v>
+        <v>-0.1875</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0823</v>
+        <v>-0.603</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.9549</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.5851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9905</v>
+        <v>-2.9892</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7737</v>
+        <v>0.2439</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2168</v>
+        <v>-3.2331</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3347</v>
+        <v>0.3003</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1769</v>
+        <v>0.286</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1578</v>
+        <v>0.0143</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6333</v>
+        <v>0.8216</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7935</v>
+        <v>0.5538</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8399</v>
+        <v>0.2677</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7013</v>
+        <v>-0.5213</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3834</v>
+        <v>-0.2679</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.318</v>
+        <v>-0.2534</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R24" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2795</v>
+        <v>0.2304</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0347</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2448</v>
+        <v>0.2208</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1952</v>
+        <v>-3.9549</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1952</v>
+        <v>-3.5851</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. ROTEGARD</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4663</v>
+        <v>-3.7535</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9419</v>
+        <v>-3.4443</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5245</v>
+        <v>-0.3092</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.5327</v>
+        <v>-2.3347</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0395</v>
+        <v>-1.1769</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5722</v>
+        <v>-1.1578</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2259</v>
+        <v>-1.6333</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6721</v>
+        <v>-0.7935</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5538</v>
+        <v>-0.8399</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3068</v>
+        <v>-0.7013</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7116</v>
+        <v>-0.3834</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0184</v>
+        <v>-0.318</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6525</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2811</v>
+        <v>0.5164</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.411</v>
+        <v>0.3641</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8702</v>
+        <v>0.1523</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.6155</v>
+        <v>-8.635400000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.926</v>
+        <v>-3.925999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.6896</v>
+        <v>-4.7092</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3425000000000005</v>
@@ -2461,10 +2461,10 @@
         <v>-1.2142</v>
       </c>
       <c r="L26" t="n">
-        <v>6.4587</v>
+        <v>6.458699999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.587000000000001</v>
+        <v>-5.587</v>
       </c>
       <c r="N26" t="n">
         <v>3.2063</v>
@@ -2482,13 +2482,13 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.7527</v>
+        <v>-1.7725</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.1388</v>
+        <v>-2.1391</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.6138</v>
+        <v>0.3662000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-4.3453</v>
